--- a/data/latest/Oil_Bulletin_Duties_and_taxes.xlsx
+++ b/data/latest/Oil_Bulletin_Duties_and_taxes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22725E1F-82B5-4A27-B2CD-00563FB9913E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0678C1BA-F261-419C-BCFA-D0E8E552106F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6675" yWindow="2160" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VAT" sheetId="4" r:id="rId1"/>
@@ -766,12 +766,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -779,6 +773,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1075,14 +1075,14 @@
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
       <c r="B1" s="15"/>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="54"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="52"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -1817,14 +1817,14 @@
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
       <c r="B1" s="34"/>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="51"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="54"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -2005,7 +2005,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="38">
-        <v>46143</v>
+        <v>46296</v>
       </c>
       <c r="C10" s="41">
         <v>514.1</v>
@@ -2079,10 +2079,10 @@
         <v>15</v>
       </c>
       <c r="B13" s="38">
-        <v>46272</v>
+        <v>46307</v>
       </c>
       <c r="C13" s="41">
-        <v>422.69</v>
+        <v>272.69</v>
       </c>
       <c r="D13" s="42">
         <v>179</v>
@@ -2411,13 +2411,13 @@
         <v>31</v>
       </c>
       <c r="B27" s="38">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="C27" s="41">
-        <v>428.15</v>
+        <v>419.48</v>
       </c>
       <c r="D27" s="42">
-        <v>264.39999999999998</v>
+        <v>265.13</v>
       </c>
       <c r="E27" s="42">
         <v>330</v>
@@ -2557,14 +2557,14 @@
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
       <c r="B1" s="34"/>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="51"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="54"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">

--- a/data/latest/Oil_Bulletin_Duties_and_taxes.xlsx
+++ b/data/latest/Oil_Bulletin_Duties_and_taxes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0678C1BA-F261-419C-BCFA-D0E8E552106F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3B9B5C-E146-4328-95EC-0D0534B56364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4455" yWindow="2610" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VAT" sheetId="4" r:id="rId1"/>
@@ -766,6 +766,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -773,12 +779,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1075,14 +1075,14 @@
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
       <c r="B1" s="15"/>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="52"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="54"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -1817,14 +1817,14 @@
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
       <c r="B1" s="34"/>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="54"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -2199,7 +2199,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="38">
-        <v>46293</v>
+        <v>46195</v>
       </c>
       <c r="C18" s="41">
         <v>139550</v>
@@ -2411,13 +2411,13 @@
         <v>31</v>
       </c>
       <c r="B27" s="38">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="C27" s="41">
-        <v>419.48</v>
+        <v>425.62</v>
       </c>
       <c r="D27" s="42">
-        <v>265.13</v>
+        <v>259.49</v>
       </c>
       <c r="E27" s="42">
         <v>330</v>
@@ -2557,14 +2557,14 @@
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
       <c r="B1" s="34"/>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="54"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">

--- a/data/latest/Oil_Bulletin_Duties_and_taxes.xlsx
+++ b/data/latest/Oil_Bulletin_Duties_and_taxes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3B9B5C-E146-4328-95EC-0D0534B56364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2A76D8-4BF2-413B-8332-912CB5B6C248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4455" yWindow="2610" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4830" yWindow="3675" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VAT" sheetId="4" r:id="rId1"/>
@@ -1955,16 +1955,16 @@
         <v>10</v>
       </c>
       <c r="B8" s="39">
-        <v>45383</v>
+        <v>46321</v>
       </c>
       <c r="C8" s="47">
-        <v>429</v>
+        <v>359</v>
       </c>
       <c r="D8" s="48">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="E8" s="48">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="F8" s="48">
         <v>15</v>
@@ -2175,13 +2175,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="38">
-        <v>46287</v>
+        <v>46321</v>
       </c>
       <c r="C17" s="41">
-        <v>397.31</v>
+        <v>407.31</v>
       </c>
       <c r="D17" s="42">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E17" s="42">
         <v>56.14</v>
@@ -2247,13 +2247,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="38">
-        <v>46300</v>
+        <v>46321</v>
       </c>
       <c r="C20" s="41">
         <v>672.9</v>
       </c>
       <c r="D20" s="42">
-        <v>622.9</v>
+        <v>572.9</v>
       </c>
       <c r="E20" s="42">
         <v>403.21000000000799</v>
@@ -2411,13 +2411,13 @@
         <v>31</v>
       </c>
       <c r="B27" s="38">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="C27" s="41">
-        <v>425.62</v>
+        <v>436.04</v>
       </c>
       <c r="D27" s="42">
-        <v>259.49</v>
+        <v>258.13</v>
       </c>
       <c r="E27" s="42">
         <v>330</v>
